--- a/sample_well_database.xlsx
+++ b/sample_well_database.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wells" sheetId="1" r:id="Rd5ff29cada444317"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecasts" sheetId="2" r:id="Rbc810fbbbca1439f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wells" sheetId="1" r:id="Ra4e8819d531d48f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecasts" sheetId="2" r:id="Rc179204ed5fd4b6b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -291,7 +291,7 @@
         <x:v>WLRC-001</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>WLRC</x:v>
+        <x:v>Formation 2</x:v>
       </x:c>
       <x:c r="C2" t="n">
         <x:v>4790000</x:v>
@@ -306,7 +306,7 @@
         <x:v>WLRC-002</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>WLRC</x:v>
+        <x:v>Formation 2</x:v>
       </x:c>
       <x:c r="C3" t="n">
         <x:v>4880000</x:v>
@@ -321,7 +321,7 @@
         <x:v>WLRC-003</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>FLHF</x:v>
+        <x:v>Formation 1</x:v>
       </x:c>
       <x:c r="C4" t="n">
         <x:v>4970000</x:v>
@@ -336,7 +336,7 @@
         <x:v>WLRC-004</x:v>
       </x:c>
       <x:c r="B5" t="str">
-        <x:v>WLRC</x:v>
+        <x:v>Formation 2</x:v>
       </x:c>
       <x:c r="C5" t="n">
         <x:v>5060000</x:v>
@@ -351,7 +351,7 @@
         <x:v>WLRC-005</x:v>
       </x:c>
       <x:c r="B6" t="str">
-        <x:v>WLRC</x:v>
+        <x:v>Formation 2</x:v>
       </x:c>
       <x:c r="C6" t="n">
         <x:v>5150000</x:v>
@@ -366,7 +366,7 @@
         <x:v>WLRC-006</x:v>
       </x:c>
       <x:c r="B7" t="str">
-        <x:v>FLHF</x:v>
+        <x:v>Formation 1</x:v>
       </x:c>
       <x:c r="C7" t="n">
         <x:v>5240000</x:v>
@@ -381,7 +381,7 @@
         <x:v>WLRC-007</x:v>
       </x:c>
       <x:c r="B8" t="str">
-        <x:v>WLRC</x:v>
+        <x:v>Formation 2</x:v>
       </x:c>
       <x:c r="C8" t="n">
         <x:v>4700000</x:v>
@@ -396,7 +396,7 @@
         <x:v>WLRC-008</x:v>
       </x:c>
       <x:c r="B9" t="str">
-        <x:v>WLRC</x:v>
+        <x:v>Formation 2</x:v>
       </x:c>
       <x:c r="C9" t="n">
         <x:v>4790000</x:v>
@@ -411,7 +411,7 @@
         <x:v>WLRC-009</x:v>
       </x:c>
       <x:c r="B10" t="str">
-        <x:v>FLHF</x:v>
+        <x:v>Formation 1</x:v>
       </x:c>
       <x:c r="C10" t="n">
         <x:v>4880000</x:v>
@@ -426,7 +426,7 @@
         <x:v>WLRC-010</x:v>
       </x:c>
       <x:c r="B11" t="str">
-        <x:v>WLRC</x:v>
+        <x:v>Formation 2</x:v>
       </x:c>
       <x:c r="C11" t="n">
         <x:v>4970000</x:v>
@@ -441,7 +441,7 @@
         <x:v>WLRC-011</x:v>
       </x:c>
       <x:c r="B12" t="str">
-        <x:v>WLRC</x:v>
+        <x:v>Formation 2</x:v>
       </x:c>
       <x:c r="C12" t="n">
         <x:v>5060000</x:v>
@@ -456,7 +456,7 @@
         <x:v>WLRC-012</x:v>
       </x:c>
       <x:c r="B13" t="str">
-        <x:v>FLHF</x:v>
+        <x:v>Formation 1</x:v>
       </x:c>
       <x:c r="C13" t="n">
         <x:v>5150000</x:v>
@@ -471,7 +471,7 @@
         <x:v>WLRC-013</x:v>
       </x:c>
       <x:c r="B14" t="str">
-        <x:v>WLRC</x:v>
+        <x:v>Formation 2</x:v>
       </x:c>
       <x:c r="C14" t="n">
         <x:v>5240000</x:v>
@@ -486,7 +486,7 @@
         <x:v>WLRC-014</x:v>
       </x:c>
       <x:c r="B15" t="str">
-        <x:v>WLRC</x:v>
+        <x:v>Formation 2</x:v>
       </x:c>
       <x:c r="C15" t="n">
         <x:v>4700000</x:v>
@@ -501,7 +501,7 @@
         <x:v>WLRC-015</x:v>
       </x:c>
       <x:c r="B16" t="str">
-        <x:v>FLHF</x:v>
+        <x:v>Formation 1</x:v>
       </x:c>
       <x:c r="C16" t="n">
         <x:v>4790000</x:v>
@@ -516,7 +516,7 @@
         <x:v>WLRC-016</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>WLRC</x:v>
+        <x:v>Formation 2</x:v>
       </x:c>
       <x:c r="C17" t="n">
         <x:v>4880000</x:v>
